--- a/artfynd/A 32645-2023 artfynd.xlsx
+++ b/artfynd/A 32645-2023 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>115323022</v>
       </c>
       <c r="B4" t="n">
-        <v>57281</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bråtebäcken (Bråtebäcken), Sm</t>
+          <t>Bråtebäcken, Bråtebäcken, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">

--- a/artfynd/A 32645-2023 artfynd.xlsx
+++ b/artfynd/A 32645-2023 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>115323022</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 32645-2023 artfynd.xlsx
+++ b/artfynd/A 32645-2023 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>115323022</v>
       </c>
       <c r="B4" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 32645-2023 artfynd.xlsx
+++ b/artfynd/A 32645-2023 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>115323022</v>
       </c>
       <c r="B4" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 32645-2023 artfynd.xlsx
+++ b/artfynd/A 32645-2023 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>115323022</v>
       </c>
       <c r="B4" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 32645-2023 artfynd.xlsx
+++ b/artfynd/A 32645-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115322697</v>
+        <v>115490419</v>
       </c>
       <c r="B2" t="n">
-        <v>78157</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bråtebäcken (Bråtebäcken), Sm</t>
+          <t>Skruvan, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535425</v>
+        <v>535416</v>
       </c>
       <c r="R2" t="n">
-        <v>6403501</v>
+        <v>6403595</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,6 +758,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,50 +777,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115322600</v>
+        <v>115322697</v>
       </c>
       <c r="B3" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bråtebäcken (Bråtebäcken), Sm</t>
+          <t>Bråtebäcken, Bråtebäcken, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535419</v>
+        <v>535425</v>
       </c>
       <c r="R3" t="n">
-        <v>6403492</v>
+        <v>6403501</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,15 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115323022</v>
+        <v>115322827</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,48 +885,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bråtebäcken, Bråtebäcken, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535422</v>
+        <v>535454</v>
       </c>
       <c r="R4" t="n">
-        <v>6403541</v>
+        <v>6403491</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -995,40 +971,44 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115323007</v>
+        <v>115323022</v>
       </c>
       <c r="B5" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>upprörd, varnande</t>
@@ -1036,7 +1016,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bråtebäcken (Bråtebäcken), Sm</t>
+          <t>Bråtebäcken, Bråtebäcken, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1102,50 +1082,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115322827</v>
+        <v>115490447</v>
       </c>
       <c r="B6" t="n">
-        <v>78157</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bråtebäcken (Bråtebäcken), Sm</t>
+          <t>Skruvan, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535454</v>
+        <v>535385</v>
       </c>
       <c r="R6" t="n">
-        <v>6403491</v>
+        <v>6403551</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1172,12 +1155,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,15 +1187,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115475103</v>
+        <v>115323007</v>
       </c>
       <c r="B7" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1238,16 +1216,21 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skruvan (Skruvan), Sm</t>
+          <t>Bråtebäcken, Bråtebäcken, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535397</v>
+        <v>535422</v>
       </c>
       <c r="R7" t="n">
-        <v>6403572</v>
+        <v>6403541</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1274,12 +1257,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1306,15 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115490432</v>
+        <v>115475103</v>
       </c>
       <c r="B8" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1340,24 +1318,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skruvan, Sm</t>
+          <t>Skruvan, Skruvan, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535392</v>
+        <v>535397</v>
       </c>
       <c r="R8" t="n">
-        <v>6403563</v>
+        <v>6403572</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1384,12 +1354,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1416,15 +1386,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115490447</v>
+        <v>115490432</v>
       </c>
       <c r="B9" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1432,31 +1397,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1464,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535385</v>
+        <v>535392</v>
       </c>
       <c r="R9" t="n">
-        <v>6403551</v>
+        <v>6403563</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1523,6 +1488,103 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>115322600</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bråtebäcken, Bråtebäcken, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>535419</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6403492</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Södra Vi</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-03-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-03-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32645-2023 artfynd.xlsx
+++ b/artfynd/A 32645-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115490419</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115322697</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115322827</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,6 +1099,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115323022</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115490447</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1286,6 +1316,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115323007</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1383,6 +1418,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115475103</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115490432</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1585,8 +1630,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115322600</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>